--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20231101_20240501.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20231101_20240501.xlsx
@@ -1097,37 +1097,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60.65573770491803</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="C16" t="n">
-        <v>39.34426229508197</v>
+        <v>41.80327868852459</v>
       </c>
       <c r="D16" t="n">
-        <v>79.67384843657983</v>
+        <v>181.9668258029544</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>INE226A01021</t>
+          <t>INE066P01011</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>-21.31147540983606</v>
+        <v>-15.57377049180327</v>
       </c>
       <c r="H16" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="I16" t="n">
         <v>75</v>
       </c>
       <c r="J16" t="n">
-        <v>1474.75</v>
+        <v>155.35</v>
       </c>
       <c r="K16" t="n">
         <v>15</v>
@@ -1141,37 +1141,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.37704918032787</v>
+        <v>61.47540983606557</v>
       </c>
       <c r="C17" t="n">
-        <v>41.80327868852459</v>
+        <v>38.52459016393443</v>
       </c>
       <c r="D17" t="n">
-        <v>181.9668258029544</v>
+        <v>73.6911321507923</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>INE066P01011</t>
+          <t>INE114A01011</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.57377049180327</v>
+        <v>-22.95081967213115</v>
       </c>
       <c r="H17" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="I17" t="n">
         <v>75</v>
       </c>
       <c r="J17" t="n">
-        <v>155.35</v>
+        <v>164.2</v>
       </c>
       <c r="K17" t="n">
         <v>16</v>
@@ -1185,37 +1185,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.47540983606557</v>
+        <v>60.65573770491803</v>
       </c>
       <c r="C18" t="n">
-        <v>38.52459016393443</v>
+        <v>39.34426229508197</v>
       </c>
       <c r="D18" t="n">
-        <v>73.6911321507923</v>
+        <v>79.67384843657983</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INE114A01011</t>
+          <t>INE226A01021</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>-22.95081967213115</v>
+        <v>-21.31147540983606</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I18" t="n">
         <v>75</v>
       </c>
       <c r="J18" t="n">
-        <v>164.2</v>
+        <v>1474.75</v>
       </c>
       <c r="K18" t="n">
         <v>17</v>
